--- a/plano_acao.xlsx
+++ b/plano_acao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/ieda_biso_terceiros_claro_com_br/Documents/Área de Trabalho/Plano de ação/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{E5717BDE-94C2-44BE-ABBE-BB2F8BE40341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3516658A-B943-45B6-A2D9-5B9A12EA26A6}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{E5717BDE-94C2-44BE-ABBE-BB2F8BE40341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D0DA0C-FF57-4E5B-B323-701C07537959}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="159">
   <si>
     <t>Número</t>
   </si>
@@ -548,6 +548,12 @@
   </si>
   <si>
     <t>Avaliar possível falha no direcionamento dos operadores do atendimento para o Televendas.</t>
+  </si>
+  <si>
+    <t>Analisar Reclamações referente ao mês de maio, com foco no Flex, Pré Pago e PME</t>
+  </si>
+  <si>
+    <t>Aumento da quantidade de reclamações no mês de maio</t>
   </si>
 </sst>
 </file>
@@ -999,17 +1005,17 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1344,10 +1350,10 @@
                   <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1728,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1806,7 +1812,7 @@
       </c>
       <c r="J2" s="6">
         <f t="shared" ref="J2:J47" ca="1" si="0">IF(I2="Concluído","",IF(G2="","",IF(TODAY()&gt;G2,TODAY()-G2,0)))</f>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K2" t="str">
         <f>IF(H2="","Não concluído",IF(H2&lt;=G2,"Concluído no prazo","Concluído fora do prazo"))</f>
@@ -1841,7 +1847,7 @@
       </c>
       <c r="J3" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K50" si="1">IF(H3="","Não concluído",IF(H3&lt;=G3,"Concluído no prazo","Concluído fora do prazo"))</f>
@@ -1876,7 +1882,7 @@
       </c>
       <c r="J4" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -2970,7 +2976,7 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -3271,7 +3277,7 @@
       </c>
       <c r="J41" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="1"/>
@@ -3459,7 +3465,7 @@
       </c>
       <c r="J46" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="1"/>
@@ -3533,7 +3539,7 @@
       </c>
       <c r="J48" s="6">
         <f t="shared" ref="J48:J50" ca="1" si="4">IF(I48="Concluído","",IF(G48="","",IF(TODAY()&gt;G48,TODAY()-G48,0)))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="1"/>
@@ -3699,7 +3705,7 @@
       <c r="H53" s="9"/>
       <c r="I53" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Em andamento</v>
+        <v>Atrasado</v>
       </c>
       <c r="J53" s="6"/>
     </row>
@@ -3728,7 +3734,7 @@
       <c r="H54" s="11"/>
       <c r="I54" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Em andamento</v>
+        <v>Atrasado</v>
       </c>
       <c r="J54" s="6"/>
     </row>
@@ -3757,13 +3763,42 @@
       <c r="H55" s="9"/>
       <c r="I55" s="11" t="str">
         <f t="shared" ca="1" si="3"/>
+        <v>Atrasado</v>
+      </c>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>53</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="13">
+        <v>46162</v>
+      </c>
+      <c r="D56" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" s="13">
+        <v>46168</v>
+      </c>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11" t="str">
+        <f t="shared" ref="I56" ca="1" si="5">IF(G56="","",IF(H56&lt;&gt;"","Concluído",IF(TODAY()&gt;G56,"Atrasado","Em andamento")))</f>
         <v>Em andamento</v>
       </c>
-      <c r="J55" s="6"/>
+      <c r="J56" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K48" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="I2:I55">
+  <conditionalFormatting sqref="I2:I56">
     <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"Concluído"</formula>
     </cfRule>
@@ -3792,19 +3827,19 @@
   <sheetData>
     <row r="1" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
         <f ca="1">COUNTA('🗂 Base'!I2:I60)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="19">
         <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Concluído")</f>
@@ -3812,15 +3847,15 @@
       </c>
       <c r="D4" s="20">
         <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Atrasado")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="21">
         <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Em Andamento")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" s="22" t="str">
         <f ca="1">IFERROR(TEXT(COUNTIF('🗂 Base'!I2:I60,"Concluído")/COUNTA('🗂 Base'!I2:I60),"0.0%"),"-")</f>
-        <v>76%</v>
+        <v>75%</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -3842,10 +3877,10 @@
     </row>
     <row r="6" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="59"/>
     </row>
     <row r="8" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
@@ -3868,7 +3903,7 @@
       </c>
       <c r="D9" s="31">
         <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I60,"Concluído")/COUNTA('🗂 Base'!I2:I60),0)</f>
-        <v>0.7592592592592593</v>
+        <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3877,11 +3912,11 @@
       </c>
       <c r="C10" s="33">
         <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Atrasado")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" s="34">
         <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I60,"Atrasado")/COUNTA('🗂 Base'!I2:I60),0)</f>
-        <v>9.2592592592592587E-2</v>
+        <v>0.14545454545454545</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3890,11 +3925,11 @@
       </c>
       <c r="C11" s="36">
         <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Em Andamento")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="37">
         <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I48,"Em Andamento")/COUNTA('🗂 Base'!I2:I60),0)</f>
-        <v>9.2592592592592587E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3903,7 +3938,7 @@
       </c>
       <c r="C12" s="39">
         <f ca="1">COUNTA('🗂 Base'!I2:I60)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="40">
         <f>100%</f>
@@ -3912,13 +3947,13 @@
     </row>
     <row r="13" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
     </row>
     <row r="15" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
@@ -3949,7 +3984,7 @@
       </c>
       <c r="E16" s="44">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,1),"")</f>
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3967,7 +4002,7 @@
       </c>
       <c r="E17" s="44">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,2),"")</f>
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3985,7 +4020,7 @@
       </c>
       <c r="E18" s="44">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,3),"")</f>
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4003,7 +4038,7 @@
       </c>
       <c r="E19" s="46">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,4),"")</f>
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4021,7 +4056,7 @@
       </c>
       <c r="E20" s="46">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,5),"")</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4039,7 +4074,7 @@
       </c>
       <c r="E21" s="46">
         <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,6),"")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4088,23 +4123,23 @@
   <sheetData>
     <row r="1" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59" t="str">
+      <c r="B3" s="57" t="str">
         <f ca="1">"Atualizado em: "&amp;TEXT(TODAY(),"DD/MM/YYYY")&amp;"   |   Total: "&amp;COUNTA('🗂 Base'!I2:I48)&amp;" ações   |   Concluídas: "&amp;COUNTIF('🗂 Base'!I2:I48,"Concluído")&amp;"   |   Atrasadas: "&amp;COUNTIF('🗂 Base'!I2:I48,"Atrasado")&amp;"   |   Em andamento: "&amp;COUNTIF('🗂 Base'!I2:I48,"Em Andamento")</f>
-        <v>Atualizado em: 18/05/YYYY   |   Total: 47 ações   |   Concluídas: 39   |   Atrasadas: 3   |   Em andamento: 5</v>
-      </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
+        <v>Atualizado em: 21/05/YYYY   |   Total: 47 ações   |   Concluídas: 39   |   Atrasadas: 3   |   Em andamento: 5</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
     </row>
     <row r="4" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="47" t="s">
@@ -4142,7 +4177,7 @@
       </c>
       <c r="F5" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J2&gt;0,'🗂 Base'!I2&amp;" ("&amp;'🗂 Base'!J2&amp;"d atraso)",'🗂 Base'!I2),"")</f>
-        <v>Em andamento (100d atraso)</v>
+        <v>Em andamento (103d atraso)</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4164,7 +4199,7 @@
       </c>
       <c r="F6" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J3&gt;0,'🗂 Base'!I3&amp;" ("&amp;'🗂 Base'!J3&amp;"d atraso)",'🗂 Base'!I3),"")</f>
-        <v>Em andamento (99d atraso)</v>
+        <v>Em andamento (102d atraso)</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4186,7 +4221,7 @@
       </c>
       <c r="F7" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J4&gt;0,'🗂 Base'!I4&amp;" ("&amp;'🗂 Base'!J4&amp;"d atraso)",'🗂 Base'!I4),"")</f>
-        <v>Em andamento (98d atraso)</v>
+        <v>Em andamento (101d atraso)</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4832,7 +4867,7 @@
       </c>
       <c r="F36" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J33&gt;0,'🗂 Base'!I33&amp;" ("&amp;'🗂 Base'!J33&amp;"d atraso)",'🗂 Base'!I33),"")</f>
-        <v>Em andamento (55d atraso)</v>
+        <v>Em andamento (58d atraso)</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5054,7 +5089,7 @@
       </c>
       <c r="F46" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J41&gt;0,'🗂 Base'!I41&amp;" ("&amp;'🗂 Base'!J41&amp;"d atraso)",'🗂 Base'!I41),"")</f>
-        <v>Em andamento (27d atraso)</v>
+        <v>Em andamento (30d atraso)</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5167,7 +5202,7 @@
       </c>
       <c r="F51" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J46&gt;0,'🗂 Base'!I46&amp;" ("&amp;'🗂 Base'!J46&amp;"d atraso)",'🗂 Base'!I46),"")</f>
-        <v>Atrasado (12d atraso)</v>
+        <v>Atrasado (15d atraso)</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5211,7 +5246,7 @@
       </c>
       <c r="F53" s="51" t="str">
         <f ca="1">IFERROR(IF('🗂 Base'!J48&gt;0,'🗂 Base'!I48&amp;" ("&amp;'🗂 Base'!J48&amp;"d atraso)",'🗂 Base'!I48),"")</f>
-        <v>Atrasado (12d atraso)</v>
+        <v>Atrasado (15d atraso)</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">

--- a/plano_acao.xlsx
+++ b/plano_acao.xlsx
@@ -5,20 +5,20 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/ieda_biso_terceiros_claro_com_br/Documents/Área de Trabalho/Plano de ação/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iedas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{E5717BDE-94C2-44BE-ABBE-BB2F8BE40341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D0DA0C-FF57-4E5B-B323-701C07537959}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80440962-7F09-4C6C-9C6D-EEFDE070E1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="🗂 Base" sheetId="1" r:id="rId1"/>
+    <sheet name="Base" sheetId="1" r:id="rId1"/>
     <sheet name="📊 Dashboard" sheetId="2" r:id="rId2"/>
     <sheet name="📋 Resumo Executivo" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'🗂 Base'!$A$1:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$K$48</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1005,17 +1005,17 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1350,10 +1350,10 @@
                   <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,10 +1549,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1812,7 +1808,7 @@
       </c>
       <c r="J2" s="6">
         <f t="shared" ref="J2:J47" ca="1" si="0">IF(I2="Concluído","",IF(G2="","",IF(TODAY()&gt;G2,TODAY()-G2,0)))</f>
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K2" t="str">
         <f>IF(H2="","Não concluído",IF(H2&lt;=G2,"Concluído no prazo","Concluído fora do prazo"))</f>
@@ -1847,7 +1843,7 @@
       </c>
       <c r="J3" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K50" si="1">IF(H3="","Não concluído",IF(H3&lt;=G3,"Concluído no prazo","Concluído fora do prazo"))</f>
@@ -1882,7 +1878,7 @@
       </c>
       <c r="J4" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -2976,7 +2972,7 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -3277,7 +3273,7 @@
       </c>
       <c r="J41" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="1"/>
@@ -3465,7 +3461,7 @@
       </c>
       <c r="J46" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="1"/>
@@ -3539,7 +3535,7 @@
       </c>
       <c r="J48" s="6">
         <f t="shared" ref="J48:J50" ca="1" si="4">IF(I48="Concluído","",IF(G48="","",IF(TODAY()&gt;G48,TODAY()-G48,0)))</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="1"/>
@@ -3792,7 +3788,7 @@
       <c r="H56" s="11"/>
       <c r="I56" s="11" t="str">
         <f t="shared" ref="I56" ca="1" si="5">IF(G56="","",IF(H56&lt;&gt;"","Concluído",IF(TODAY()&gt;G56,"Atrasado","Em andamento")))</f>
-        <v>Em andamento</v>
+        <v>Atrasado</v>
       </c>
       <c r="J56" s="6"/>
     </row>
@@ -3827,34 +3823,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
-        <f ca="1">COUNTA('🗂 Base'!I2:I60)</f>
+        <f ca="1">COUNTA(Base!I2:I60)</f>
         <v>55</v>
       </c>
       <c r="C4" s="19">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Concluído")</f>
+        <f ca="1">COUNTIF(Base!I2:I60,"Concluído")</f>
         <v>41</v>
       </c>
       <c r="D4" s="20">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Atrasado")</f>
-        <v>8</v>
+        <f ca="1">COUNTIF(Base!I2:I60,"Atrasado")</f>
+        <v>9</v>
       </c>
       <c r="E4" s="21">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Em Andamento")</f>
-        <v>6</v>
+        <f ca="1">COUNTIF(Base!I2:I60,"Em Andamento")</f>
+        <v>5</v>
       </c>
       <c r="F4" s="22" t="str">
-        <f ca="1">IFERROR(TEXT(COUNTIF('🗂 Base'!I2:I60,"Concluído")/COUNTA('🗂 Base'!I2:I60),"0.0%"),"-")</f>
+        <f ca="1">IFERROR(TEXT(COUNTIF(Base!I2:I60,"Concluído")/COUNTA(Base!I2:I60),"0.0%"),"-")</f>
         <v>75%</v>
       </c>
     </row>
@@ -3877,10 +3873,10 @@
     </row>
     <row r="6" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="59"/>
+      <c r="C7" s="57"/>
     </row>
     <row r="8" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
@@ -3898,11 +3894,11 @@
         <v>30</v>
       </c>
       <c r="C9" s="30">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Concluído")</f>
+        <f ca="1">COUNTIF(Base!I2:I60,"Concluído")</f>
         <v>41</v>
       </c>
       <c r="D9" s="31">
-        <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I60,"Concluído")/COUNTA('🗂 Base'!I2:I60),0)</f>
+        <f ca="1">IFERROR(COUNTIF(Base!I2:I60,"Concluído")/COUNTA(Base!I2:I60),0)</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
@@ -3911,12 +3907,12 @@
         <v>11</v>
       </c>
       <c r="C10" s="33">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Atrasado")</f>
-        <v>8</v>
+        <f ca="1">COUNTIF(Base!I2:I60,"Atrasado")</f>
+        <v>9</v>
       </c>
       <c r="D10" s="34">
-        <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I60,"Atrasado")/COUNTA('🗂 Base'!I2:I60),0)</f>
-        <v>0.14545454545454545</v>
+        <f ca="1">IFERROR(COUNTIF(Base!I2:I60,"Atrasado")/COUNTA(Base!I2:I60),0)</f>
+        <v>0.16363636363636364</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3924,11 +3920,11 @@
         <v>13</v>
       </c>
       <c r="C11" s="36">
-        <f ca="1">COUNTIF('🗂 Base'!I2:I60,"Em Andamento")</f>
-        <v>6</v>
+        <f ca="1">COUNTIF(Base!I2:I60,"Em Andamento")</f>
+        <v>5</v>
       </c>
       <c r="D11" s="37">
-        <f ca="1">IFERROR(COUNTIF('🗂 Base'!I2:I48,"Em Andamento")/COUNTA('🗂 Base'!I2:I60),0)</f>
+        <f ca="1">IFERROR(COUNTIF(Base!I2:I48,"Em Andamento")/COUNTA(Base!I2:I60),0)</f>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
@@ -3937,7 +3933,7 @@
         <v>132</v>
       </c>
       <c r="C12" s="39">
-        <f ca="1">COUNTA('🗂 Base'!I2:I60)</f>
+        <f ca="1">COUNTA(Base!I2:I60)</f>
         <v>55</v>
       </c>
       <c r="D12" s="40">
@@ -3947,13 +3943,13 @@
     </row>
     <row r="13" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
     </row>
     <row r="15" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="28" t="s">
@@ -3971,110 +3967,110 @@
     </row>
     <row r="16" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D2:D48,MATCH(LARGE('🗂 Base'!J2:J60,1),'🗂 Base'!J2:J60,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D2:D48,MATCH(LARGE(Base!J2:J60,1),Base!J2:J60,0)),70),"-")</f>
         <v>PROTOCOLO DE CONFLITOS NÃO GERADOS PARA O BKO PORTABILIDADE (No fecham</v>
       </c>
       <c r="C16" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F2:F60,MATCH(LARGE('🗂 Base'!J2:J60,1),'🗂 Base'!J2:J60,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F2:F60,MATCH(LARGE(Base!J2:J60,1),Base!J2:J60,0)),"-")</f>
         <v>Guilherme Carrasco</v>
       </c>
       <c r="D16" s="43">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G60,MATCH(LARGE('🗂 Base'!J2:J60,1),'🗂 Base'!J2:J60,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G60,MATCH(LARGE(Base!J2:J60,1),Base!J2:J60,0)),"-")</f>
         <v>46060</v>
       </c>
       <c r="E16" s="44">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,1),"")</f>
-        <v>103</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,1),"")</f>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D3:D49,MATCH(LARGE('🗂 Base'!J3:J61,1),'🗂 Base'!J3:J61,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D3:D49,MATCH(LARGE(Base!J3:J61,1),Base!J3:J61,0)),70),"-")</f>
         <v>PROTOCOLO DE CONFLITOS NÃO GERADOS PARA O BKO PORTABILIDADE (No fecham</v>
       </c>
       <c r="C17" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F3:F61,MATCH(LARGE('🗂 Base'!J3:J61,1),'🗂 Base'!J3:J61,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F3:F61,MATCH(LARGE(Base!J3:J61,1),Base!J3:J61,0)),"-")</f>
         <v>Fauzi</v>
       </c>
       <c r="D17" s="43">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G60,MATCH(LARGE('🗂 Base'!J2:J48,2),'🗂 Base'!J2:J48,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G60,MATCH(LARGE(Base!J2:J48,2),Base!J2:J48,0)),"-")</f>
         <v>46061</v>
       </c>
       <c r="E17" s="44">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,2),"")</f>
-        <v>102</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,2),"")</f>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D4:D50,MATCH(LARGE('🗂 Base'!J4:J62,1),'🗂 Base'!J4:J62,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D4:D50,MATCH(LARGE(Base!J4:J62,1),Base!J4:J62,0)),70),"-")</f>
         <v xml:space="preserve">SAP – PORTABILIDADE INTERNA (Na reunião de portabilidade realizada em </v>
       </c>
       <c r="C18" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F4:F62,MATCH(LARGE('🗂 Base'!J4:J62,1),'🗂 Base'!J4:J62,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F4:F62,MATCH(LARGE(Base!J4:J62,1),Base!J4:J62,0)),"-")</f>
         <v>Janaina Cruz</v>
       </c>
       <c r="D18" s="43">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G48,MATCH(LARGE('🗂 Base'!J2:J60,3),'🗂 Base'!J2:J48,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G48,MATCH(LARGE(Base!J2:J60,3),Base!J2:J48,0)),"-")</f>
         <v>46062</v>
       </c>
       <c r="E18" s="44">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,3),"")</f>
-        <v>101</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,3),"")</f>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D5:D51,MATCH(LARGE('🗂 Base'!J5:J63,1),'🗂 Base'!J5:J63,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D5:D51,MATCH(LARGE(Base!J5:J63,1),Base!J5:J63,0)),70),"-")</f>
         <v>PORTABILIDADE INTERNA- Demanda skill preferencial</v>
       </c>
       <c r="C19" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F5:F63,MATCH(LARGE('🗂 Base'!J5:J63,1),'🗂 Base'!J5:J63,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F5:F63,MATCH(LARGE(Base!J5:J63,1),Base!J5:J63,0)),"-")</f>
         <v>Diego</v>
       </c>
       <c r="D19" s="45">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G48,MATCH(LARGE('🗂 Base'!J2:J48,4),'🗂 Base'!J2:J60,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G48,MATCH(LARGE(Base!J2:J48,4),Base!J2:J60,0)),"-")</f>
         <v>46105</v>
       </c>
       <c r="E19" s="46">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,4),"")</f>
-        <v>58</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,4),"")</f>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D6:D52,MATCH(LARGE('🗂 Base'!J6:J64,1),'🗂 Base'!J6:J64,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D6:D52,MATCH(LARGE(Base!J6:J64,1),Base!J6:J64,0)),70),"-")</f>
         <v>PORTABILIDADE INTERNA- Demanda skill preferencial</v>
       </c>
       <c r="C20" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F6:F64,MATCH(LARGE('🗂 Base'!J6:J64,1),'🗂 Base'!J6:J64,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F6:F64,MATCH(LARGE(Base!J6:J64,1),Base!J6:J64,0)),"-")</f>
         <v>Diego</v>
       </c>
       <c r="D20" s="45">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G48,MATCH(LARGE('🗂 Base'!J2:J48,5),'🗂 Base'!J2:J48,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G48,MATCH(LARGE(Base!J2:J48,5),Base!J2:J48,0)),"-")</f>
         <v>46133</v>
       </c>
       <c r="E20" s="46">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,5),"")</f>
-        <v>30</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,5),"")</f>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="41" t="str">
-        <f ca="1">IFERROR(LEFT(INDEX('🗂 Base'!D7:D53,MATCH(LARGE('🗂 Base'!J7:J65,1),'🗂 Base'!J7:J65,0)),70),"-")</f>
+        <f ca="1">IFERROR(LEFT(INDEX(Base!D7:D53,MATCH(LARGE(Base!J7:J65,1),Base!J7:J65,0)),70),"-")</f>
         <v>PORTABILIDADE INTERNA- Demanda skill preferencial</v>
       </c>
       <c r="C21" s="42" t="str">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!F7:F65,MATCH(LARGE('🗂 Base'!J7:J65,1),'🗂 Base'!J7:J65,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!F7:F65,MATCH(LARGE(Base!J7:J65,1),Base!J7:J65,0)),"-")</f>
         <v>Diego</v>
       </c>
       <c r="D21" s="45">
-        <f ca="1">IFERROR(INDEX('🗂 Base'!G2:G48,MATCH(LARGE('🗂 Base'!J2:J48,6),'🗂 Base'!J2:J48,0)),"-")</f>
+        <f ca="1">IFERROR(INDEX(Base!G2:G48,MATCH(LARGE(Base!J2:J48,6),Base!J2:J48,0)),"-")</f>
         <v>46148</v>
       </c>
       <c r="E21" s="46">
-        <f ca="1">IFERROR(LARGE('🗂 Base'!J2:J48,6),"")</f>
-        <v>15</v>
+        <f ca="1">IFERROR(LARGE(Base!J2:J48,6),"")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4123,23 +4119,23 @@
   <sheetData>
     <row r="1" spans="2:6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="57" t="str">
-        <f ca="1">"Atualizado em: "&amp;TEXT(TODAY(),"DD/MM/YYYY")&amp;"   |   Total: "&amp;COUNTA('🗂 Base'!I2:I48)&amp;" ações   |   Concluídas: "&amp;COUNTIF('🗂 Base'!I2:I48,"Concluído")&amp;"   |   Atrasadas: "&amp;COUNTIF('🗂 Base'!I2:I48,"Atrasado")&amp;"   |   Em andamento: "&amp;COUNTIF('🗂 Base'!I2:I48,"Em Andamento")</f>
-        <v>Atualizado em: 21/05/YYYY   |   Total: 47 ações   |   Concluídas: 39   |   Atrasadas: 3   |   Em andamento: 5</v>
-      </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
+      <c r="B3" s="59" t="str">
+        <f ca="1">"Atualizado em: "&amp;TEXT(TODAY(),"DD/MM/YYYY")&amp;"   |   Total: "&amp;COUNTA(Base!I2:I48)&amp;" ações   |   Concluídas: "&amp;COUNTIF(Base!I2:I48,"Concluído")&amp;"   |   Atrasadas: "&amp;COUNTIF(Base!I2:I48,"Atrasado")&amp;"   |   Em andamento: "&amp;COUNTIF(Base!I2:I48,"Em Andamento")</f>
+        <v>Atualizado em: 29/05/YYYY   |   Total: 47 ações   |   Concluídas: 39   |   Atrasadas: 3   |   Em andamento: 5</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="47" t="s">
@@ -4160,1114 +4156,1114 @@
     </row>
     <row r="5" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D2,85),"")</f>
+        <f>IFERROR(LEFT(Base!D2,85),"")</f>
         <v>PROTOCOLO DE CONFLITOS NÃO GERADOS PARA O BKO PORTABILIDADE (No fechamento de novembr</v>
       </c>
       <c r="C5" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E2,130),"")</f>
+        <f>IFERROR(LEFT(Base!E2,130),"")</f>
         <v>Aberto chamado PDST-2228261 para investigação com equipe do Guilherme Carrasco_x000B_</v>
       </c>
       <c r="D5" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F2,"")</f>
+        <f>IFERROR(Base!F2,"")</f>
         <v>Guilherme Carrasco</v>
       </c>
       <c r="E5" s="50">
-        <f>IFERROR('🗂 Base'!G2,"-")</f>
+        <f>IFERROR(Base!G2,"-")</f>
         <v>46060</v>
       </c>
       <c r="F5" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J2&gt;0,'🗂 Base'!I2&amp;" ("&amp;'🗂 Base'!J2&amp;"d atraso)",'🗂 Base'!I2),"")</f>
-        <v>Em andamento (103d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J2&gt;0,Base!I2&amp;" ("&amp;Base!J2&amp;"d atraso)",Base!I2),"")</f>
+        <v>Em andamento (111d atraso)</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D3,85),"")</f>
+        <f>IFERROR(LEFT(Base!D3,85),"")</f>
         <v>PROTOCOLO DE CONFLITOS NÃO GERADOS PARA O BKO PORTABILIDADE (No fechamento de novembr</v>
       </c>
       <c r="C6" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E3,130),"")</f>
+        <f>IFERROR(LEFT(Base!E3,130),"")</f>
         <v>Ter alarme para sinalizar falha na integração entre SPN e PS8.</v>
       </c>
       <c r="D6" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F3,"")</f>
+        <f>IFERROR(Base!F3,"")</f>
         <v>Fauzi</v>
       </c>
       <c r="E6" s="50">
-        <f>IFERROR('🗂 Base'!G3,"-")</f>
+        <f>IFERROR(Base!G3,"-")</f>
         <v>46061</v>
       </c>
       <c r="F6" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J3&gt;0,'🗂 Base'!I3&amp;" ("&amp;'🗂 Base'!J3&amp;"d atraso)",'🗂 Base'!I3),"")</f>
-        <v>Em andamento (102d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J3&gt;0,Base!I3&amp;" ("&amp;Base!J3&amp;"d atraso)",Base!I3),"")</f>
+        <v>Em andamento (110d atraso)</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D4,85),"")</f>
+        <f>IFERROR(LEFT(Base!D4,85),"")</f>
         <v>SAP – PORTABILIDADE INTERNA (Na reunião de portabilidade realizada em 09/12, foi info</v>
       </c>
       <c r="C7" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E4,130),"")</f>
+        <f>IFERROR(LEFT(Base!E4,130),"")</f>
         <v>Aberto PDST-2245268 para investigação com time de OGS (TI). No SAP apresenta a mensagem: “Operadora Doadora auto-preenchida deve s</v>
       </c>
       <c r="D7" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F4,"")</f>
+        <f>IFERROR(Base!F4,"")</f>
         <v>Janaina Cruz</v>
       </c>
       <c r="E7" s="50">
-        <f>IFERROR('🗂 Base'!G4,"-")</f>
+        <f>IFERROR(Base!G4,"-")</f>
         <v>46062</v>
       </c>
       <c r="F7" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J4&gt;0,'🗂 Base'!I4&amp;" ("&amp;'🗂 Base'!J4&amp;"d atraso)",'🗂 Base'!I4),"")</f>
-        <v>Em andamento (101d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J4&gt;0,Base!I4&amp;" ("&amp;Base!J4&amp;"d atraso)",Base!I4),"")</f>
+        <v>Em andamento (109d atraso)</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D5,85),"")</f>
+        <f>IFERROR(LEFT(Base!D5,85),"")</f>
         <v>Link do site não esta funcionando de maneira correta</v>
       </c>
       <c r="C8" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E5,130),"")</f>
+        <f>IFERROR(LEFT(Base!E5,130),"")</f>
         <v xml:space="preserve">Avaliação e correção do link de status de portabilidade no site </v>
       </c>
       <c r="D8" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F5,"")</f>
+        <f>IFERROR(Base!F5,"")</f>
         <v>Tânia</v>
       </c>
       <c r="E8" s="50">
-        <f>IFERROR('🗂 Base'!G5,"-")</f>
+        <f>IFERROR(Base!G5,"-")</f>
         <v>46050</v>
       </c>
       <c r="F8" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J5&gt;0,'🗂 Base'!I5&amp;" ("&amp;'🗂 Base'!J5&amp;"d atraso)",'🗂 Base'!I5),"")</f>
+        <f ca="1">IFERROR(IF(Base!J5&gt;0,Base!I5&amp;" ("&amp;Base!J5&amp;"d atraso)",Base!I5),"")</f>
         <v>Atrasado</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D6,85),"")</f>
+        <f>IFERROR(LEFT(Base!D6,85),"")</f>
         <v>Reunião Portabilidade</v>
       </c>
       <c r="C9" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E6,130),"")</f>
+        <f>IFERROR(LEFT(Base!E6,130),"")</f>
         <v>Reforço da comunicação para vendedores e áreas de suporte sobre o fluxo de entrega de chip</v>
       </c>
       <c r="D9" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F6,"")</f>
+        <f>IFERROR(Base!F6,"")</f>
         <v>Viviane e Natalia</v>
       </c>
       <c r="E9" s="50">
-        <f>IFERROR('🗂 Base'!G6,"-")</f>
+        <f>IFERROR(Base!G6,"-")</f>
         <v>46050</v>
       </c>
       <c r="F9" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J6&gt;0,'🗂 Base'!I6&amp;" ("&amp;'🗂 Base'!J6&amp;"d atraso)",'🗂 Base'!I6),"")</f>
+        <f ca="1">IFERROR(IF(Base!J6&gt;0,Base!I6&amp;" ("&amp;Base!J6&amp;"d atraso)",Base!I6),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D7,85),"")</f>
+        <f>IFERROR(LEFT(Base!D7,85),"")</f>
         <v xml:space="preserve">Apresentação dos indicadores </v>
       </c>
       <c r="C10" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E7,130),"")</f>
+        <f>IFERROR(LEFT(Base!E7,130),"")</f>
         <v xml:space="preserve">Acompanhamento dos indicadores de reagendamento e ocorrências aos finais de semana, com retorno em próxima agenda </v>
       </c>
       <c r="D10" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F7,"")</f>
+        <f>IFERROR(Base!F7,"")</f>
         <v>Cícera e Galvão</v>
       </c>
       <c r="E10" s="50">
-        <f>IFERROR('🗂 Base'!G7,"-")</f>
+        <f>IFERROR(Base!G7,"-")</f>
         <v>46050</v>
       </c>
       <c r="F10" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J7&gt;0,'🗂 Base'!I7&amp;" ("&amp;'🗂 Base'!J7&amp;"d atraso)",'🗂 Base'!I7),"")</f>
+        <f ca="1">IFERROR(IF(Base!J7&gt;0,Base!I7&amp;" ("&amp;Base!J7&amp;"d atraso)",Base!I7),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D8,85),"")</f>
+        <f>IFERROR(LEFT(Base!D8,85),"")</f>
         <v>Instabilidades de DDD 6XX / Chip</v>
       </c>
       <c r="C11" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E8,130),"")</f>
+        <f>IFERROR(LEFT(Base!E8,130),"")</f>
         <v>Acompanhar chamado casos DDD 6XX  acompanhar os testes com BKO técnico</v>
       </c>
       <c r="D11" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F8,"")</f>
+        <f>IFERROR(Base!F8,"")</f>
         <v>Diego</v>
       </c>
       <c r="E11" s="50">
-        <f>IFERROR('🗂 Base'!G8,"-")</f>
+        <f>IFERROR(Base!G8,"-")</f>
         <v>46057</v>
       </c>
       <c r="F11" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J8&gt;0,'🗂 Base'!I8&amp;" ("&amp;'🗂 Base'!J8&amp;"d atraso)",'🗂 Base'!I8),"")</f>
+        <f ca="1">IFERROR(IF(Base!J8&gt;0,Base!I8&amp;" ("&amp;Base!J8&amp;"d atraso)",Base!I8),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D9,85),"")</f>
+        <f>IFERROR(LEFT(Base!D9,85),"")</f>
         <v>DDP OS160257</v>
       </c>
       <c r="C12" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E9,130),"")</f>
+        <f>IFERROR(LEFT(Base!E9,130),"")</f>
         <v>TI implantar a correção do sincronismo SPN x BR - Aline verificar prazo com TI</v>
       </c>
       <c r="D12" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F9,"")</f>
+        <f>IFERROR(Base!F9,"")</f>
         <v>Aline</v>
       </c>
       <c r="E12" s="50">
-        <f>IFERROR('🗂 Base'!G9,"-")</f>
+        <f>IFERROR(Base!G9,"-")</f>
         <v>46057</v>
       </c>
       <c r="F12" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J9&gt;0,'🗂 Base'!I9&amp;" ("&amp;'🗂 Base'!J9&amp;"d atraso)",'🗂 Base'!I9),"")</f>
+        <f ca="1">IFERROR(IF(Base!J9&gt;0,Base!I9&amp;" ("&amp;Base!J9&amp;"d atraso)",Base!I9),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D10,85),"")</f>
+        <f>IFERROR(LEFT(Base!D10,85),"")</f>
         <v>Bilhete cancelado</v>
       </c>
       <c r="C13" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E10,130),"")</f>
+        <f>IFERROR(LEFT(Base!E10,130),"")</f>
         <v>Ajustar lógica de envio de SMS em bilhetes cancelados - Aline verificar com ABR</v>
       </c>
       <c r="D13" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F10,"")</f>
+        <f>IFERROR(Base!F10,"")</f>
         <v>Aline</v>
       </c>
       <c r="E13" s="50">
-        <f>IFERROR('🗂 Base'!G10,"-")</f>
+        <f>IFERROR(Base!G10,"-")</f>
         <v>46057</v>
       </c>
       <c r="F13" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J10&gt;0,'🗂 Base'!I10&amp;" ("&amp;'🗂 Base'!J10&amp;"d atraso)",'🗂 Base'!I10),"")</f>
+        <f ca="1">IFERROR(IF(Base!J10&gt;0,Base!I10&amp;" ("&amp;Base!J10&amp;"d atraso)",Base!I10),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D11,85),"")</f>
+        <f>IFERROR(LEFT(Base!D11,85),"")</f>
         <v>Ativação CHIP</v>
       </c>
       <c r="C14" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E11,130),"")</f>
+        <f>IFERROR(LEFT(Base!E11,130),"")</f>
         <v>Validar qual é o processo oficial quando o cliente procura a loja solicitando ajuda para ativar o chip, garantindo padronização no</v>
       </c>
       <c r="D14" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F11,"")</f>
+        <f>IFERROR(Base!F11,"")</f>
         <v xml:space="preserve">  - Borges e Vivi Becker</v>
       </c>
       <c r="E14" s="50">
-        <f>IFERROR('🗂 Base'!G11,"-")</f>
+        <f>IFERROR(Base!G11,"-")</f>
         <v>46057</v>
       </c>
       <c r="F14" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J11&gt;0,'🗂 Base'!I11&amp;" ("&amp;'🗂 Base'!J11&amp;"d atraso)",'🗂 Base'!I11),"")</f>
+        <f ca="1">IFERROR(IF(Base!J11&gt;0,Base!I11&amp;" ("&amp;Base!J11&amp;"d atraso)",Base!I11),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D12,85),"")</f>
+        <f>IFERROR(LEFT(Base!D12,85),"")</f>
         <v>Ativação CHIP</v>
       </c>
       <c r="C15" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E12,130),"")</f>
+        <f>IFERROR(LEFT(Base!E12,130),"")</f>
         <v>Garantir que as informações estejam claras no SIM Card e no Kit Welcome, evitando dúvidas durante o atendimento. </v>
       </c>
       <c r="D15" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F12,"")</f>
+        <f>IFERROR(Base!F12,"")</f>
         <v>Marketing</v>
       </c>
       <c r="E15" s="50">
-        <f>IFERROR('🗂 Base'!G12,"-")</f>
+        <f>IFERROR(Base!G12,"-")</f>
         <v>46057</v>
       </c>
       <c r="F15" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J12&gt;0,'🗂 Base'!I12&amp;" ("&amp;'🗂 Base'!J12&amp;"d atraso)",'🗂 Base'!I12),"")</f>
+        <f ca="1">IFERROR(IF(Base!J12&gt;0,Base!I12&amp;" ("&amp;Base!J12&amp;"d atraso)",Base!I12),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D13,85),"")</f>
+        <f>IFERROR(LEFT(Base!D13,85),"")</f>
         <v>Ativação CHIP</v>
       </c>
       <c r="C16" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E13,130),"")</f>
+        <f>IFERROR(LEFT(Base!E13,130),"")</f>
         <v>Confirmar se o conteúdo orientativo está disponível para a equipe de atendimento, e identificar onde esse material está localizado</v>
       </c>
       <c r="D16" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F13,"")</f>
+        <f>IFERROR(Base!F13,"")</f>
         <v xml:space="preserve">  - Borges e Vivi Becker</v>
       </c>
       <c r="E16" s="50">
-        <f>IFERROR('🗂 Base'!G13,"-")</f>
+        <f>IFERROR(Base!G13,"-")</f>
         <v>46058</v>
       </c>
       <c r="F16" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J13&gt;0,'🗂 Base'!I13&amp;" ("&amp;'🗂 Base'!J13&amp;"d atraso)",'🗂 Base'!I13),"")</f>
+        <f ca="1">IFERROR(IF(Base!J13&gt;0,Base!I13&amp;" ("&amp;Base!J13&amp;"d atraso)",Base!I13),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D14,85),"")</f>
+        <f>IFERROR(LEFT(Base!D14,85),"")</f>
         <v>Instabilidades de DDD 6XX / Chip</v>
       </c>
       <c r="C17" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E14,130),"")</f>
+        <f>IFERROR(LEFT(Base!E14,130),"")</f>
         <v xml:space="preserve">Realizar Rastreamento do caso DDD6X, para identificar causa raiz e realizar abrangência para garantir que não tenha mais lote não </v>
       </c>
       <c r="D17" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F14,"")</f>
+        <f>IFERROR(Base!F14,"")</f>
         <v>Hebert</v>
       </c>
       <c r="E17" s="50">
-        <f>IFERROR('🗂 Base'!G14,"-")</f>
+        <f>IFERROR(Base!G14,"-")</f>
         <v>46064</v>
       </c>
       <c r="F17" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J14&gt;0,'🗂 Base'!I14&amp;" ("&amp;'🗂 Base'!J14&amp;"d atraso)",'🗂 Base'!I14),"")</f>
+        <f ca="1">IFERROR(IF(Base!J14&gt;0,Base!I14&amp;" ("&amp;Base!J14&amp;"d atraso)",Base!I14),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D15,85),"")</f>
+        <f>IFERROR(LEFT(Base!D15,85),"")</f>
         <v>Instabilidades de DDD 6XX / Chip</v>
       </c>
       <c r="C18" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E15,130),"")</f>
+        <f>IFERROR(LEFT(Base!E15,130),"")</f>
         <v>Executar plano de substituição conforme fluxo definido e acompanha impacto do lote DDD6X</v>
       </c>
       <c r="D18" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F15,"")</f>
+        <f>IFERROR(Base!F15,"")</f>
         <v>Diego</v>
       </c>
       <c r="E18" s="50">
-        <f>IFERROR('🗂 Base'!G15,"-")</f>
+        <f>IFERROR(Base!G15,"-")</f>
         <v>46064</v>
       </c>
       <c r="F18" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J15&gt;0,'🗂 Base'!I15&amp;" ("&amp;'🗂 Base'!J15&amp;"d atraso)",'🗂 Base'!I15),"")</f>
+        <f ca="1">IFERROR(IF(Base!J15&gt;0,Base!I15&amp;" ("&amp;Base!J15&amp;"d atraso)",Base!I15),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D16,85),"")</f>
+        <f>IFERROR(LEFT(Base!D16,85),"")</f>
         <v>DDP DDPs 160749 e 160750 Falha Atualização do Status do Bilhete</v>
       </c>
       <c r="C19" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E16,130),"")</f>
+        <f>IFERROR(LEFT(Base!E16,130),"")</f>
         <v>Validar geração de protocolo pós-tratativa OGS e confirmar regularização do fluxo BKO</v>
       </c>
       <c r="D19" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F16,"")</f>
+        <f>IFERROR(Base!F16,"")</f>
         <v>Rogerio Galvão</v>
       </c>
       <c r="E19" s="50">
-        <f>IFERROR('🗂 Base'!G16,"-")</f>
+        <f>IFERROR(Base!G16,"-")</f>
         <v>46073</v>
       </c>
       <c r="F19" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J16&gt;0,'🗂 Base'!I16&amp;" ("&amp;'🗂 Base'!J16&amp;"d atraso)",'🗂 Base'!I16),"")</f>
+        <f ca="1">IFERROR(IF(Base!J16&gt;0,Base!I16&amp;" ("&amp;Base!J16&amp;"d atraso)",Base!I16),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D17,85),"")</f>
+        <f>IFERROR(LEFT(Base!D17,85),"")</f>
         <v>Reunião Portabilidade</v>
       </c>
       <c r="C20" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E17,130),"")</f>
+        <f>IFERROR(LEFT(Base!E17,130),"")</f>
         <v>Verificar com André Sbarai a revisão do fluxo de atendimento</v>
       </c>
       <c r="D20" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F17,"")</f>
+        <f>IFERROR(Base!F17,"")</f>
         <v>Diego</v>
       </c>
       <c r="E20" s="50">
-        <f>IFERROR('🗂 Base'!G17,"-")</f>
+        <f>IFERROR(Base!G17,"-")</f>
         <v>46073</v>
       </c>
       <c r="F20" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J17&gt;0,'🗂 Base'!I17&amp;" ("&amp;'🗂 Base'!J17&amp;"d atraso)",'🗂 Base'!I17),"")</f>
+        <f ca="1">IFERROR(IF(Base!J17&gt;0,Base!I17&amp;" ("&amp;Base!J17&amp;"d atraso)",Base!I17),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D18,85),"")</f>
+        <f>IFERROR(LEFT(Base!D18,85),"")</f>
         <v>Indicador de reclamações alto na semana 7</v>
       </c>
       <c r="C21" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E18,130),"")</f>
+        <f>IFERROR(LEFT(Base!E18,130),"")</f>
         <v>Acompanhar indicadores de CPF divergente</v>
       </c>
       <c r="D21" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F18,"")</f>
+        <f>IFERROR(Base!F18,"")</f>
         <v xml:space="preserve"> Rogerio Galvão</v>
       </c>
       <c r="E21" s="50">
-        <f>IFERROR('🗂 Base'!G18,"-")</f>
+        <f>IFERROR(Base!G18,"-")</f>
         <v>46073</v>
       </c>
       <c r="F21" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J18&gt;0,'🗂 Base'!I18&amp;" ("&amp;'🗂 Base'!J18&amp;"d atraso)",'🗂 Base'!I18),"")</f>
+        <f ca="1">IFERROR(IF(Base!J18&gt;0,Base!I18&amp;" ("&amp;Base!J18&amp;"d atraso)",Base!I18),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D19,85),"")</f>
+        <f>IFERROR(LEFT(Base!D19,85),"")</f>
         <v>PA Qualificadora</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E19,130),"")</f>
+        <f>IFERROR(LEFT(Base!E19,130),"")</f>
         <v>obter a fotografia do dia em que os clientes acionaram a PA
 Conforme retorno do Diego não é possível incluir a informação do dia d</v>
       </c>
       <c r="D22" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F19,"")</f>
+        <f>IFERROR(Base!F19,"")</f>
         <v>Diego</v>
       </c>
       <c r="E22" s="50">
-        <f>IFERROR('🗂 Base'!G19,"-")</f>
+        <f>IFERROR(Base!G19,"-")</f>
         <v>46073</v>
       </c>
       <c r="F22" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J19&gt;0,'🗂 Base'!I19&amp;" ("&amp;'🗂 Base'!J19&amp;"d atraso)",'🗂 Base'!I19),"")</f>
+        <f ca="1">IFERROR(IF(Base!J19&gt;0,Base!I19&amp;" ("&amp;Base!J19&amp;"d atraso)",Base!I19),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D20,85),"")</f>
+        <f>IFERROR(LEFT(Base!D20,85),"")</f>
         <v xml:space="preserve">Qual fluxo adotado quando o token de CPF divergente não funciona.
 -, o BKO direciona </v>
       </c>
       <c r="C23" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E20,130),"")</f>
+        <f>IFERROR(LEFT(Base!E20,130),"")</f>
         <v>Validar procedimento oficial do fluxo a ser realizado quando o token não foi ativado.</v>
       </c>
       <c r="D23" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F20,"")</f>
+        <f>IFERROR(Base!F20,"")</f>
         <v xml:space="preserve"> Rogerio Galvão</v>
       </c>
       <c r="E23" s="50">
-        <f>IFERROR('🗂 Base'!G20,"-")</f>
+        <f>IFERROR(Base!G20,"-")</f>
         <v>46085</v>
       </c>
       <c r="F23" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J20&gt;0,'🗂 Base'!I20&amp;" ("&amp;'🗂 Base'!J20&amp;"d atraso)",'🗂 Base'!I20),"")</f>
+        <f ca="1">IFERROR(IF(Base!J20&gt;0,Base!I20&amp;" ("&amp;Base!J20&amp;"d atraso)",Base!I20),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D21,85),"")</f>
+        <f>IFERROR(LEFT(Base!D21,85),"")</f>
         <v>Indicadores</v>
       </c>
       <c r="C24" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E21,130),"")</f>
+        <f>IFERROR(LEFT(Base!E21,130),"")</f>
         <v>Analisar verbatins de reclamações Pré-Pago (jan/fev) para identificar causa raiz.</v>
       </c>
       <c r="D24" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F21,"")</f>
+        <f>IFERROR(Base!F21,"")</f>
         <v>Daniela</v>
       </c>
       <c r="E24" s="50">
-        <f>IFERROR('🗂 Base'!G21,"-")</f>
+        <f>IFERROR(Base!G21,"-")</f>
         <v>46085</v>
       </c>
       <c r="F24" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J21&gt;0,'🗂 Base'!I21&amp;" ("&amp;'🗂 Base'!J21&amp;"d atraso)",'🗂 Base'!I21),"")</f>
+        <f ca="1">IFERROR(IF(Base!J21&gt;0,Base!I21&amp;" ("&amp;Base!J21&amp;"d atraso)",Base!I21),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D22,85),"")</f>
+        <f>IFERROR(LEFT(Base!D22,85),"")</f>
         <v>Indicadores</v>
       </c>
       <c r="C25" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E22,130),"")</f>
+        <f>IFERROR(LEFT(Base!E22,130),"")</f>
         <v>Avaliar casos de Portabilidade Não Cancelada.</v>
       </c>
       <c r="D25" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F22,"")</f>
+        <f>IFERROR(Base!F22,"")</f>
         <v>Diego</v>
       </c>
       <c r="E25" s="50">
-        <f>IFERROR('🗂 Base'!G22,"-")</f>
+        <f>IFERROR(Base!G22,"-")</f>
         <v>46085</v>
       </c>
       <c r="F25" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J22&gt;0,'🗂 Base'!I22&amp;" ("&amp;'🗂 Base'!J22&amp;"d atraso)",'🗂 Base'!I22),"")</f>
+        <f ca="1">IFERROR(IF(Base!J22&gt;0,Base!I22&amp;" ("&amp;Base!J22&amp;"d atraso)",Base!I22),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D23,85),"")</f>
+        <f>IFERROR(LEFT(Base!D23,85),"")</f>
         <v>PORTABILIDADE INTERNA
 Identificada falha no fluxo de Portin Interno . Nos casos Singl</v>
       </c>
       <c r="C26" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E23,130),"")</f>
+        <f>IFERROR(LEFT(Base!E23,130),"")</f>
         <v>Abrir nova demanda para Mailing Portin Interno para direcionamento URA SKill Preferencial.</v>
       </c>
       <c r="D26" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F23,"")</f>
+        <f>IFERROR(Base!F23,"")</f>
         <v>Diego</v>
       </c>
       <c r="E26" s="50">
-        <f>IFERROR('🗂 Base'!G23,"-")</f>
+        <f>IFERROR(Base!G23,"-")</f>
         <v>46092</v>
       </c>
       <c r="F26" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J23&gt;0,'🗂 Base'!I23&amp;" ("&amp;'🗂 Base'!J23&amp;"d atraso)",'🗂 Base'!I23),"")</f>
+        <f ca="1">IFERROR(IF(Base!J23&gt;0,Base!I23&amp;" ("&amp;Base!J23&amp;"d atraso)",Base!I23),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D24,85),"")</f>
+        <f>IFERROR(LEFT(Base!D24,85),"")</f>
         <v>Casos Pré Pago</v>
       </c>
       <c r="C27" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E24,130),"")</f>
+        <f>IFERROR(LEFT(Base!E24,130),"")</f>
         <v>Apresentação da avaliação amostral clientes canal Anatel próxima reunião dia 11/03. Respon. :Daniela</v>
       </c>
       <c r="D27" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F24,"")</f>
+        <f>IFERROR(Base!F24,"")</f>
         <v>Dani Vieira</v>
       </c>
       <c r="E27" s="50">
-        <f>IFERROR('🗂 Base'!G24,"-")</f>
+        <f>IFERROR(Base!G24,"-")</f>
         <v>46092</v>
       </c>
       <c r="F27" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J24&gt;0,'🗂 Base'!I24&amp;" ("&amp;'🗂 Base'!J24&amp;"d atraso)",'🗂 Base'!I24),"")</f>
+        <f ca="1">IFERROR(IF(Base!J24&gt;0,Base!I24&amp;" ("&amp;Base!J24&amp;"d atraso)",Base!I24),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D25,85),"")</f>
+        <f>IFERROR(LEFT(Base!D25,85),"")</f>
         <v>Portabilidade Sem Bilhete
 O cliente entra no atendimento sem bilhete de portabilidade</v>
       </c>
       <c r="C28" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E25,130),"")</f>
+        <f>IFERROR(LEFT(Base!E25,130),"")</f>
         <v>Verificar se existe procedimento para tratativa de clientes sem bilhete de portabilidade no atendimento.</v>
       </c>
       <c r="D28" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F25,"")</f>
+        <f>IFERROR(Base!F25,"")</f>
         <v>Diego/Antonio</v>
       </c>
       <c r="E28" s="50">
-        <f>IFERROR('🗂 Base'!G25,"-")</f>
+        <f>IFERROR(Base!G25,"-")</f>
         <v>46099</v>
       </c>
       <c r="F28" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J25&gt;0,'🗂 Base'!I25&amp;" ("&amp;'🗂 Base'!J25&amp;"d atraso)",'🗂 Base'!I25),"")</f>
+        <f ca="1">IFERROR(IF(Base!J25&gt;0,Base!I25&amp;" ("&amp;Base!J25&amp;"d atraso)",Base!I25),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D26,85),"")</f>
+        <f>IFERROR(LEFT(Base!D26,85),"")</f>
         <v>PORTABILIDADE INTERNA
 de clientes com Portout na Nucell e portin para Claro, onde o c</v>
       </c>
       <c r="C29" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E26,130),"")</f>
+        <f>IFERROR(LEFT(Base!E26,130),"")</f>
         <v xml:space="preserve">Priorização da abertura do Mailing para direcionamento na Ura do Skill preferencial. </v>
       </c>
       <c r="D29" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F26,"")</f>
+        <f>IFERROR(Base!F26,"")</f>
         <v>Diego</v>
       </c>
       <c r="E29" s="50">
-        <f>IFERROR('🗂 Base'!G26,"-")</f>
+        <f>IFERROR(Base!G26,"-")</f>
         <v>46099</v>
       </c>
       <c r="F29" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J26&gt;0,'🗂 Base'!I26&amp;" ("&amp;'🗂 Base'!J26&amp;"d atraso)",'🗂 Base'!I26),"")</f>
+        <f ca="1">IFERROR(IF(Base!J26&gt;0,Base!I26&amp;" ("&amp;Base!J26&amp;"d atraso)",Base!I26),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D27,85),"")</f>
+        <f>IFERROR(LEFT(Base!D27,85),"")</f>
         <v>PORTABILIDADE INTERNA
 de clientes com Portout na Nucell e portin para Claro, onde o c</v>
       </c>
       <c r="C30" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E27,130),"")</f>
+        <f>IFERROR(LEFT(Base!E27,130),"")</f>
         <v>Enviar demanda que foi escrita pelo Hugo para acompanhamento da Portabilidade Interna.</v>
       </c>
       <c r="D30" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F27,"")</f>
+        <f>IFERROR(Base!F27,"")</f>
         <v>Aline</v>
       </c>
       <c r="E30" s="50">
-        <f>IFERROR('🗂 Base'!G27,"-")</f>
+        <f>IFERROR(Base!G27,"-")</f>
         <v>46092</v>
       </c>
       <c r="F30" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J27&gt;0,'🗂 Base'!I27&amp;" ("&amp;'🗂 Base'!J27&amp;"d atraso)",'🗂 Base'!I27),"")</f>
+        <f ca="1">IFERROR(IF(Base!J27&gt;0,Base!I27&amp;" ("&amp;Base!J27&amp;"d atraso)",Base!I27),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D28,85),"")</f>
+        <f>IFERROR(LEFT(Base!D28,85),"")</f>
         <v>BKO sinalizou volume de protocolos abaixo do esperado na operação.</v>
       </c>
       <c r="C31" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E28,130),"")</f>
+        <f>IFERROR(LEFT(Base!E28,130),"")</f>
         <v>Avaliar desvio do volume de protocolo com o time BCC e o João.</v>
       </c>
       <c r="D31" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F28,"")</f>
+        <f>IFERROR(Base!F28,"")</f>
         <v>Galvão</v>
       </c>
       <c r="E31" s="50">
-        <f>IFERROR('🗂 Base'!G28,"-")</f>
+        <f>IFERROR(Base!G28,"-")</f>
         <v>46092</v>
       </c>
       <c r="F31" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J28&gt;0,'🗂 Base'!I28&amp;" ("&amp;'🗂 Base'!J28&amp;"d atraso)",'🗂 Base'!I28),"")</f>
+        <f ca="1">IFERROR(IF(Base!J28&gt;0,Base!I28&amp;" ("&amp;Base!J28&amp;"d atraso)",Base!I28),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D29,85),"")</f>
+        <f>IFERROR(LEFT(Base!D29,85),"")</f>
         <v xml:space="preserve">
  Cliente teve bilhete portabilidade cancelado em loja, no qual ocorreram inconsistên</v>
       </c>
       <c r="C32" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E29,130),"")</f>
+        <f>IFERROR(LEFT(Base!E29,130),"")</f>
         <v>Montar plano de ação com o time Borges para treinamento e calibração das lojas. Responsável: Natalia</v>
       </c>
       <c r="D32" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F29,"")</f>
+        <f>IFERROR(Base!F29,"")</f>
         <v>Natalia</v>
       </c>
       <c r="E32" s="50">
-        <f>IFERROR('🗂 Base'!G29,"-")</f>
+        <f>IFERROR(Base!G29,"-")</f>
         <v>46105</v>
       </c>
       <c r="F32" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J29&gt;0,'🗂 Base'!I29&amp;" ("&amp;'🗂 Base'!J29&amp;"d atraso)",'🗂 Base'!I29),"")</f>
+        <f ca="1">IFERROR(IF(Base!J29&gt;0,Base!I29&amp;" ("&amp;Base!J29&amp;"d atraso)",Base!I29),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D30,85),"")</f>
+        <f>IFERROR(LEFT(Base!D30,85),"")</f>
         <v>Portabilidade e Sobreposição de Canais:
 Casos em que a janela de portabilidade foi co</v>
       </c>
       <c r="C33" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E30,130),"")</f>
+        <f>IFERROR(LEFT(Base!E30,130),"")</f>
         <v>Analisar motivo da não efetivação da sobreposição</v>
       </c>
       <c r="D33" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F30,"")</f>
+        <f>IFERROR(Base!F30,"")</f>
         <v>Janaina/ OGS</v>
       </c>
       <c r="E33" s="50">
-        <f>IFERROR('🗂 Base'!G30,"-")</f>
+        <f>IFERROR(Base!G30,"-")</f>
         <v>46105</v>
       </c>
       <c r="F33" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J30&gt;0,'🗂 Base'!I30&amp;" ("&amp;'🗂 Base'!J30&amp;"d atraso)",'🗂 Base'!I30),"")</f>
+        <f ca="1">IFERROR(IF(Base!J30&gt;0,Base!I30&amp;" ("&amp;Base!J30&amp;"d atraso)",Base!I30),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D31,85),"")</f>
+        <f>IFERROR(LEFT(Base!D31,85),"")</f>
         <v>Aumento manifestações da Anatel</v>
       </c>
       <c r="C34" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E31,130),"")</f>
+        <f>IFERROR(LEFT(Base!E31,130),"")</f>
         <v>Avaliar entrega de chip.</v>
       </c>
       <c r="D34" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F31,"")</f>
+        <f>IFERROR(Base!F31,"")</f>
         <v>Ednalva</v>
       </c>
       <c r="E34" s="50">
-        <f>IFERROR('🗂 Base'!G31,"-")</f>
+        <f>IFERROR(Base!G31,"-")</f>
         <v>46105</v>
       </c>
       <c r="F34" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J31&gt;0,'🗂 Base'!I31&amp;" ("&amp;'🗂 Base'!J31&amp;"d atraso)",'🗂 Base'!I31),"")</f>
+        <f ca="1">IFERROR(IF(Base!J31&gt;0,Base!I31&amp;" ("&amp;Base!J31&amp;"d atraso)",Base!I31),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D32,85),"")</f>
+        <f>IFERROR(LEFT(Base!D32,85),"")</f>
         <v>Aumento manifestações da Anatel</v>
       </c>
       <c r="C35" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E32,130),"")</f>
+        <f>IFERROR(LEFT(Base!E32,130),"")</f>
         <v>Agendar reunião específica para processo de portabilidade sem bilhete</v>
       </c>
       <c r="D35" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F32,"")</f>
+        <f>IFERROR(Base!F32,"")</f>
         <v>Diego</v>
       </c>
       <c r="E35" s="50">
-        <f>IFERROR('🗂 Base'!G32,"-")</f>
+        <f>IFERROR(Base!G32,"-")</f>
         <v>46105</v>
       </c>
       <c r="F35" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J32&gt;0,'🗂 Base'!I32&amp;" ("&amp;'🗂 Base'!J32&amp;"d atraso)",'🗂 Base'!I32),"")</f>
+        <f ca="1">IFERROR(IF(Base!J32&gt;0,Base!I32&amp;" ("&amp;Base!J32&amp;"d atraso)",Base!I32),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D33,85),"")</f>
+        <f>IFERROR(LEFT(Base!D33,85),"")</f>
         <v>PORTABILIDADE INTERNA- Demanda skill preferencial</v>
       </c>
       <c r="C36" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E33,130),"")</f>
+        <f>IFERROR(LEFT(Base!E33,130),"")</f>
         <v>Abertura de demanda no Hike para maling de direcionamento de Portabilidade Interna para o Skill preferencial.</v>
       </c>
       <c r="D36" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F33,"")</f>
+        <f>IFERROR(Base!F33,"")</f>
         <v>Diego</v>
       </c>
       <c r="E36" s="50">
-        <f>IFERROR('🗂 Base'!G33,"-")</f>
+        <f>IFERROR(Base!G33,"-")</f>
         <v>46105</v>
       </c>
       <c r="F36" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J33&gt;0,'🗂 Base'!I33&amp;" ("&amp;'🗂 Base'!J33&amp;"d atraso)",'🗂 Base'!I33),"")</f>
-        <v>Em andamento (58d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J33&gt;0,Base!I33&amp;" ("&amp;Base!J33&amp;"d atraso)",Base!I33),"")</f>
+        <v>Em andamento (66d atraso)</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D34,85),"")</f>
+        <f>IFERROR(LEFT(Base!D34,85),"")</f>
         <v>Implantação da melhoria nas mensagens do sistema ativação simplificada eliminando men</v>
       </c>
       <c r="C37" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E34,130),"")</f>
+        <f>IFERROR(LEFT(Base!E34,130),"")</f>
         <v xml:space="preserve">Enviar comunicado para os canais de vendas. </v>
       </c>
       <c r="D37" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F34,"")</f>
+        <f>IFERROR(Base!F34,"")</f>
         <v>Viviane</v>
       </c>
       <c r="E37" s="50">
-        <f>IFERROR('🗂 Base'!G34,"-")</f>
+        <f>IFERROR(Base!G34,"-")</f>
         <v>46105</v>
       </c>
       <c r="F37" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J34&gt;0,'🗂 Base'!I34&amp;" ("&amp;'🗂 Base'!J34&amp;"d atraso)",'🗂 Base'!I34),"")</f>
+        <f ca="1">IFERROR(IF(Base!J34&gt;0,Base!I34&amp;" ("&amp;Base!J34&amp;"d atraso)",Base!I34),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D35,85),"")</f>
+        <f>IFERROR(LEFT(Base!D35,85),"")</f>
         <v>PA Qualificadora</v>
       </c>
       <c r="C38" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E35,130),"")</f>
+        <f>IFERROR(LEFT(Base!E35,130),"")</f>
         <v>Envio da PA Qualificcadora</v>
       </c>
       <c r="D38" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F35,"")</f>
+        <f>IFERROR(Base!F35,"")</f>
         <v>Diego</v>
       </c>
       <c r="E38" s="50">
-        <f>IFERROR('🗂 Base'!G35,"-")</f>
+        <f>IFERROR(Base!G35,"-")</f>
         <v>46108</v>
       </c>
       <c r="F38" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J35&gt;0,'🗂 Base'!I35&amp;" ("&amp;'🗂 Base'!J35&amp;"d atraso)",'🗂 Base'!I35),"")</f>
+        <f ca="1">IFERROR(IF(Base!J35&gt;0,Base!I35&amp;" ("&amp;Base!J35&amp;"d atraso)",Base!I35),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D36,85),"")</f>
+        <f>IFERROR(LEFT(Base!D36,85),"")</f>
         <v>Processos nas Lojas
  Clientes relataram que vendedores estão retendo o chip, o que im</v>
       </c>
       <c r="C39" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E36,130),"")</f>
+        <f>IFERROR(LEFT(Base!E36,130),"")</f>
         <v>Publicar comunicado de reforço por 3 semanas card em 24/03 (nº 1323505931) e haverá reforço operacional junto a vendedores e geren</v>
       </c>
       <c r="D39" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F36,"")</f>
+        <f>IFERROR(Base!F36,"")</f>
         <v>Natalia</v>
       </c>
       <c r="E39" s="50">
-        <f>IFERROR('🗂 Base'!G36,"-")</f>
+        <f>IFERROR(Base!G36,"-")</f>
         <v>46113</v>
       </c>
       <c r="F39" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J36&gt;0,'🗂 Base'!I36&amp;" ("&amp;'🗂 Base'!J36&amp;"d atraso)",'🗂 Base'!I36),"")</f>
+        <f ca="1">IFERROR(IF(Base!J36&gt;0,Base!I36&amp;" ("&amp;Base!J36&amp;"d atraso)",Base!I36),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D37,85),"")</f>
+        <f>IFERROR(LEFT(Base!D37,85),"")</f>
         <v>Sistema Ativação Simplificada</v>
       </c>
       <c r="C40" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E37,130),"")</f>
+        <f>IFERROR(LEFT(Base!E37,130),"")</f>
         <v>Envio do comunicado sobre Mensagens de Portabilidade no Sistema Ativação Simplificada para todos os canais.</v>
       </c>
       <c r="D40" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F37,"")</f>
+        <f>IFERROR(Base!F37,"")</f>
         <v>Vivi</v>
       </c>
       <c r="E40" s="50">
-        <f>IFERROR('🗂 Base'!G37,"-")</f>
+        <f>IFERROR(Base!G37,"-")</f>
         <v>46105</v>
       </c>
       <c r="F40" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J37&gt;0,'🗂 Base'!I37&amp;" ("&amp;'🗂 Base'!J37&amp;"d atraso)",'🗂 Base'!I37),"")</f>
+        <f ca="1">IFERROR(IF(Base!J37&gt;0,Base!I37&amp;" ("&amp;Base!J37&amp;"d atraso)",Base!I37),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D38,85),"")</f>
+        <f>IFERROR(LEFT(Base!D38,85),"")</f>
         <v>Portabilidade e Sobreposição
 Solicitação de portabilidade de Pré Pago para sobrepor u</v>
       </c>
       <c r="C41" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E38,130),"")</f>
+        <f>IFERROR(LEFT(Base!E38,130),"")</f>
         <v xml:space="preserve">Identificar possíveis causas operacionais ou sistêmicas </v>
       </c>
       <c r="D41" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F38,"")</f>
+        <f>IFERROR(Base!F38,"")</f>
         <v>Borges</v>
       </c>
       <c r="E41" s="50">
-        <f>IFERROR('🗂 Base'!G38,"-")</f>
+        <f>IFERROR(Base!G38,"-")</f>
         <v>46115</v>
       </c>
       <c r="F41" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J38&gt;0,'🗂 Base'!I38&amp;" ("&amp;'🗂 Base'!J38&amp;"d atraso)",'🗂 Base'!I38),"")</f>
+        <f ca="1">IFERROR(IF(Base!J38&gt;0,Base!I38&amp;" ("&amp;Base!J38&amp;"d atraso)",Base!I38),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D39,85),"")</f>
+        <f>IFERROR(LEFT(Base!D39,85),"")</f>
         <v>Aumento de conflitos de CPF divergente sem tratamento em loja, principalmente em clie</v>
       </c>
       <c r="C42" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E39,130),"")</f>
+        <f>IFERROR(LEFT(Base!E39,130),"")</f>
         <v>1. Verificar se há alguma falha sistêmica</v>
       </c>
       <c r="D42" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F39,"")</f>
+        <f>IFERROR(Base!F39,"")</f>
         <v>Borges</v>
       </c>
       <c r="E42" s="50">
-        <f>IFERROR('🗂 Base'!G39,"-")</f>
+        <f>IFERROR(Base!G39,"-")</f>
         <v>46115</v>
       </c>
       <c r="F42" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J39&gt;0,'🗂 Base'!I39&amp;" ("&amp;'🗂 Base'!J39&amp;"d atraso)",'🗂 Base'!I39),"")</f>
+        <f ca="1">IFERROR(IF(Base!J39&gt;0,Base!I39&amp;" ("&amp;Base!J39&amp;"d atraso)",Base!I39),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D40,85),"")</f>
+        <f>IFERROR(LEFT(Base!D40,85),"")</f>
         <v>Aumento de conflitos de CPF divergente sem tratamento em loja, principalmente em clie</v>
       </c>
       <c r="C43" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E40,130),"")</f>
+        <f>IFERROR(LEFT(Base!E40,130),"")</f>
         <v>2. Caso não seja verificado erro sistêmico, será realizado reforço pontual, comunicado e, se necessário, visita às lojas.</v>
       </c>
       <c r="D43" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F40,"")</f>
+        <f>IFERROR(Base!F40,"")</f>
         <v>Natalia</v>
       </c>
       <c r="E43" s="50">
-        <f>IFERROR('🗂 Base'!G40,"-")</f>
+        <f>IFERROR(Base!G40,"-")</f>
         <v>46115</v>
       </c>
       <c r="F43" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J40&gt;0,'🗂 Base'!I40&amp;" ("&amp;'🗂 Base'!J40&amp;"d atraso)",'🗂 Base'!I40),"")</f>
+        <f ca="1">IFERROR(IF(Base!J40&gt;0,Base!I40&amp;" ("&amp;Base!J40&amp;"d atraso)",Base!I40),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,85),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,85),"")</f>
         <v/>
       </c>
       <c r="C44" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,130),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,130),"")</f>
         <v/>
       </c>
       <c r="D44" s="49" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"")</f>
+        <f>IFERROR(Base!#REF!,"")</f>
         <v/>
       </c>
       <c r="E44" s="50" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"-")</f>
+        <f>IFERROR(Base!#REF!,"-")</f>
         <v>-</v>
       </c>
       <c r="F44" s="51" t="str">
-        <f>IFERROR(IF('🗂 Base'!#REF!&gt;0,'🗂 Base'!#REF!&amp;" ("&amp;'🗂 Base'!#REF!&amp;"d atraso)",'🗂 Base'!#REF!),"")</f>
+        <f>IFERROR(IF(Base!#REF!&gt;0,Base!#REF!&amp;" ("&amp;Base!#REF!&amp;"d atraso)",Base!#REF!),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,85),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,85),"")</f>
         <v/>
       </c>
       <c r="C45" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,130),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,130),"")</f>
         <v/>
       </c>
       <c r="D45" s="49" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"")</f>
+        <f>IFERROR(Base!#REF!,"")</f>
         <v/>
       </c>
       <c r="E45" s="50" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"-")</f>
+        <f>IFERROR(Base!#REF!,"-")</f>
         <v>-</v>
       </c>
       <c r="F45" s="51" t="str">
-        <f>IFERROR(IF('🗂 Base'!#REF!&gt;0,'🗂 Base'!#REF!&amp;" ("&amp;'🗂 Base'!#REF!&amp;"d atraso)",'🗂 Base'!#REF!),"")</f>
+        <f>IFERROR(IF(Base!#REF!&gt;0,Base!#REF!&amp;" ("&amp;Base!#REF!&amp;"d atraso)",Base!#REF!),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D41,85),"")</f>
+        <f>IFERROR(LEFT(Base!D41,85),"")</f>
         <v>CANCELAMENTO NÃO REALIZADO (Conforme análise de verbatins dos clientes, existem muita</v>
       </c>
       <c r="C46" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E41,130),"")</f>
+        <f>IFERROR(LEFT(Base!E41,130),"")</f>
         <v>Ampliar análise de casos de cancelamento não realizado para maior assertividade.</v>
       </c>
       <c r="D46" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F41,"")</f>
+        <f>IFERROR(Base!F41,"")</f>
         <v>Diego</v>
       </c>
       <c r="E46" s="50">
-        <f>IFERROR('🗂 Base'!G41,"-")</f>
+        <f>IFERROR(Base!G41,"-")</f>
         <v>46133</v>
       </c>
       <c r="F46" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J41&gt;0,'🗂 Base'!I41&amp;" ("&amp;'🗂 Base'!J41&amp;"d atraso)",'🗂 Base'!I41),"")</f>
-        <v>Em andamento (30d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J41&gt;0,Base!I41&amp;" ("&amp;Base!J41&amp;"d atraso)",Base!I41),"")</f>
+        <v>Em andamento (38d atraso)</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D42,85),"")</f>
+        <f>IFERROR(LEFT(Base!D42,85),"")</f>
         <v>Token Anatel</v>
       </c>
       <c r="C47" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E42,130),"")</f>
+        <f>IFERROR(LEFT(Base!E42,130),"")</f>
         <v>Selecionar e documentar casos de Token ANATEL (Ativação Simplificada) para abertura de chamado.</v>
       </c>
       <c r="D47" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F42,"")</f>
+        <f>IFERROR(Base!F42,"")</f>
         <v>Cristiane</v>
       </c>
       <c r="E47" s="50">
-        <f>IFERROR('🗂 Base'!G42,"-")</f>
+        <f>IFERROR(Base!G42,"-")</f>
         <v>46133</v>
       </c>
       <c r="F47" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J42&gt;0,'🗂 Base'!I42&amp;" ("&amp;'🗂 Base'!J42&amp;"d atraso)",'🗂 Base'!I42),"")</f>
+        <f ca="1">IFERROR(IF(Base!J42&gt;0,Base!I42&amp;" ("&amp;Base!J42&amp;"d atraso)",Base!I42),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D43,85),"")</f>
+        <f>IFERROR(LEFT(Base!D43,85),"")</f>
         <v>Lentidão SPN (Token e Bilhete)
 Atraso em relação aos bilhetes e token da ABR</v>
       </c>
       <c r="C48" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E43,130),"")</f>
+        <f>IFERROR(LEFT(Base!E43,130),"")</f>
         <v>Continuar monitorando possíveis ocorrências de lentidão no SPN, especialmente em janelas de pico, com foco em bilhete, reagendamen</v>
       </c>
       <c r="D48" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F43,"")</f>
+        <f>IFERROR(Base!F43,"")</f>
         <v>Galvão, Roldão, Diego e Cícera</v>
       </c>
       <c r="E48" s="50">
-        <f>IFERROR('🗂 Base'!G43,"-")</f>
+        <f>IFERROR(Base!G43,"-")</f>
         <v>46142</v>
       </c>
       <c r="F48" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J43&gt;0,'🗂 Base'!I43&amp;" ("&amp;'🗂 Base'!J43&amp;"d atraso)",'🗂 Base'!I43),"")</f>
+        <f ca="1">IFERROR(IF(Base!J43&gt;0,Base!I43&amp;" ("&amp;Base!J43&amp;"d atraso)",Base!I43),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D44,85),"")</f>
+        <f>IFERROR(LEFT(Base!D44,85),"")</f>
         <v>Chamado ABR – SPN / Token
 Atraso em relação aos bilhetes e token da ABR</v>
       </c>
       <c r="C49" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E44,130),"")</f>
+        <f>IFERROR(LEFT(Base!E44,130),"")</f>
         <v>Acompanhar o chamado junto à ABR e reforçar a cobrança para identificação da causa raiz, visando evitar novos impactos operacionai</v>
       </c>
       <c r="D49" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F44,"")</f>
+        <f>IFERROR(Base!F44,"")</f>
         <v>Aline</v>
       </c>
       <c r="E49" s="50">
-        <f>IFERROR('🗂 Base'!G44,"-")</f>
+        <f>IFERROR(Base!G44,"-")</f>
         <v>46142</v>
       </c>
       <c r="F49" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J44&gt;0,'🗂 Base'!I44&amp;" ("&amp;'🗂 Base'!J44&amp;"d atraso)",'🗂 Base'!I44),"")</f>
+        <f ca="1">IFERROR(IF(Base!J44&gt;0,Base!I44&amp;" ("&amp;Base!J44&amp;"d atraso)",Base!I44),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D45,85),"")</f>
+        <f>IFERROR(LEFT(Base!D45,85),"")</f>
         <v>Flex – Portabilidade Não Realizada
 Foi identificado que o sistema não estava enviando</v>
       </c>
       <c r="C50" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E45,130),"")</f>
+        <f>IFERROR(LEFT(Base!E45,130),"")</f>
         <v xml:space="preserve">Avaliar se a falha no envio do código para logística, decorrente da migração do SAP, está impactando o aumento das reclamações de </v>
       </c>
       <c r="D50" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F45,"")</f>
+        <f>IFERROR(Base!F45,"")</f>
         <v>Ieda</v>
       </c>
       <c r="E50" s="50">
-        <f>IFERROR('🗂 Base'!G45,"-")</f>
+        <f>IFERROR(Base!G45,"-")</f>
         <v>46142</v>
       </c>
       <c r="F50" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J45&gt;0,'🗂 Base'!I45&amp;" ("&amp;'🗂 Base'!J45&amp;"d atraso)",'🗂 Base'!I45),"")</f>
+        <f ca="1">IFERROR(IF(Base!J45&gt;0,Base!I45&amp;" ("&amp;Base!J45&amp;"d atraso)",Base!I45),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D46,85),"")</f>
+        <f>IFERROR(LEFT(Base!D46,85),"")</f>
         <v>Foram discutidos casos de clientes em processo de portabilidade que não receberam o c</v>
       </c>
       <c r="C51" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E46,130),"")</f>
+        <f>IFERROR(LEFT(Base!E46,130),"")</f>
         <v>Realizar reunião de alinhamento sobre casos MVNO sem chip e definição de devolução/estorno.</v>
       </c>
       <c r="D51" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F46,"")</f>
+        <f>IFERROR(Base!F46,"")</f>
         <v>Tania</v>
       </c>
       <c r="E51" s="50">
-        <f>IFERROR('🗂 Base'!G46,"-")</f>
+        <f>IFERROR(Base!G46,"-")</f>
         <v>46148</v>
       </c>
       <c r="F51" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J46&gt;0,'🗂 Base'!I46&amp;" ("&amp;'🗂 Base'!J46&amp;"d atraso)",'🗂 Base'!I46),"")</f>
-        <v>Atrasado (15d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J46&gt;0,Base!I46&amp;" ("&amp;Base!J46&amp;"d atraso)",Base!I46),"")</f>
+        <v>Atrasado (23d atraso)</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D47,85),"")</f>
+        <f>IFERROR(LEFT(Base!D47,85),"")</f>
         <v>A ABR foi acionada no final de semana devido a instabilidades, durante uma manutenção</v>
       </c>
       <c r="C52" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E47,130),"")</f>
+        <f>IFERROR(LEFT(Base!E47,130),"")</f>
         <v>Acionar TI para cobrança de prazo e tratamento da lentidão interna.</v>
       </c>
       <c r="D52" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F47,"")</f>
+        <f>IFERROR(Base!F47,"")</f>
         <v>Aline</v>
       </c>
       <c r="E52" s="50">
-        <f>IFERROR('🗂 Base'!G47,"-")</f>
+        <f>IFERROR(Base!G47,"-")</f>
         <v>46148</v>
       </c>
       <c r="F52" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J47&gt;0,'🗂 Base'!I47&amp;" ("&amp;'🗂 Base'!J47&amp;"d atraso)",'🗂 Base'!I47),"")</f>
+        <f ca="1">IFERROR(IF(Base!J47&gt;0,Base!I47&amp;" ("&amp;Base!J47&amp;"d atraso)",Base!I47),"")</f>
         <v>Concluído (d atraso)</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!D48,85),"")</f>
+        <f>IFERROR(LEFT(Base!D48,85),"")</f>
         <v>Foi discutido sobre os planos de ações em andamento relacionados ao cliente em loja p</v>
       </c>
       <c r="C53" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!E48,130),"")</f>
+        <f>IFERROR(LEFT(Base!E48,130),"")</f>
         <v xml:space="preserve">Definir e comunicar data do workshop em lojas. </v>
       </c>
       <c r="D53" s="49" t="str">
-        <f>IFERROR('🗂 Base'!F48,"")</f>
+        <f>IFERROR(Base!F48,"")</f>
         <v>Borges</v>
       </c>
       <c r="E53" s="50">
-        <f>IFERROR('🗂 Base'!G48,"-")</f>
+        <f>IFERROR(Base!G48,"-")</f>
         <v>46148</v>
       </c>
       <c r="F53" s="51" t="str">
-        <f ca="1">IFERROR(IF('🗂 Base'!J48&gt;0,'🗂 Base'!I48&amp;" ("&amp;'🗂 Base'!J48&amp;"d atraso)",'🗂 Base'!I48),"")</f>
-        <v>Atrasado (15d atraso)</v>
+        <f ca="1">IFERROR(IF(Base!J48&gt;0,Base!I48&amp;" ("&amp;Base!J48&amp;"d atraso)",Base!I48),"")</f>
+        <v>Atrasado (23d atraso)</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,85),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,85),"")</f>
         <v/>
       </c>
       <c r="C54" s="48" t="str">
-        <f>IFERROR(LEFT('🗂 Base'!#REF!,130),"")</f>
+        <f>IFERROR(LEFT(Base!#REF!,130),"")</f>
         <v/>
       </c>
       <c r="D54" s="49" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"")</f>
+        <f>IFERROR(Base!#REF!,"")</f>
         <v/>
       </c>
       <c r="E54" s="50" t="str">
-        <f>IFERROR('🗂 Base'!#REF!,"-")</f>
+        <f>IFERROR(Base!#REF!,"-")</f>
         <v>-</v>
       </c>
       <c r="F54" s="51" t="str">
-        <f>IFERROR(IF('🗂 Base'!#REF!&gt;0,'🗂 Base'!#REF!&amp;" ("&amp;'🗂 Base'!#REF!&amp;"d atraso)",'🗂 Base'!#REF!),"")</f>
+        <f>IFERROR(IF(Base!#REF!&gt;0,Base!#REF!&amp;" ("&amp;Base!#REF!&amp;"d atraso)",Base!#REF!),"")</f>
         <v/>
       </c>
     </row>
